--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>125630629</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>125630629</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>125630629</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>125630629</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>125630629</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>125630629</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>125630629</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>125630629</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>126869412</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>126868956</v>
       </c>
       <c r="B5" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126869314</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126869643</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>126869425</v>
       </c>
       <c r="B8" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126869537</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>126868998</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126869103</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>126869574</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>126869327</v>
       </c>
       <c r="B16" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,46 +2301,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126869039</v>
+        <v>126869396</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>91284</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2348,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516968</v>
+        <v>516879</v>
       </c>
       <c r="R17" t="n">
-        <v>6705769</v>
+        <v>6705823</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2384,11 +2375,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,37 +2402,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126869396</v>
+        <v>126869039</v>
       </c>
       <c r="B18" t="n">
-        <v>91210</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516879</v>
+        <v>516968</v>
       </c>
       <c r="R18" t="n">
-        <v>6705823</v>
+        <v>6705769</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2490,6 +2485,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,7 +2520,7 @@
         <v>126869551</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>126869457</v>
       </c>
       <c r="B20" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126869384</v>
+        <v>126869056</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>91319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,31 +2748,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516872</v>
+        <v>516953</v>
       </c>
       <c r="R21" t="n">
-        <v>6705794</v>
+        <v>6705765</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2818,17 +2813,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2847,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126869056</v>
+        <v>126869384</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2858,26 +2849,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2885,10 +2881,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516953</v>
+        <v>516872</v>
       </c>
       <c r="R22" t="n">
-        <v>6705765</v>
+        <v>6705794</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2923,13 +2919,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>126869412</v>
       </c>
       <c r="B4" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>126868956</v>
       </c>
       <c r="B5" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126869314</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126869643</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>126869425</v>
       </c>
       <c r="B8" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126869537</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>126868998</v>
       </c>
       <c r="B11" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126869103</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,46 +1980,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126869574</v>
+        <v>126869237</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516694</v>
+        <v>516915</v>
       </c>
       <c r="R14" t="n">
-        <v>6705877</v>
+        <v>6705768</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2065,13 +2061,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2090,42 +2090,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126869237</v>
+        <v>126869574</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2133,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516915</v>
+        <v>516694</v>
       </c>
       <c r="R15" t="n">
-        <v>6705768</v>
+        <v>6705877</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2171,17 +2175,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>126869327</v>
       </c>
       <c r="B16" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,37 +2301,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126869396</v>
+        <v>126869039</v>
       </c>
       <c r="B17" t="n">
-        <v>91284</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2339,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516879</v>
+        <v>516968</v>
       </c>
       <c r="R17" t="n">
-        <v>6705823</v>
+        <v>6705769</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2375,6 +2384,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,46 +2416,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126869039</v>
+        <v>126869396</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>91290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516968</v>
+        <v>516879</v>
       </c>
       <c r="R18" t="n">
-        <v>6705769</v>
+        <v>6705823</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2485,11 +2490,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,7 +2520,7 @@
         <v>126869551</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>126869457</v>
       </c>
       <c r="B20" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>126869056</v>
       </c>
       <c r="B21" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126869425</v>
+        <v>126869537</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,26 +1349,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516854</v>
+        <v>516717</v>
       </c>
       <c r="R8" t="n">
-        <v>6705833</v>
+        <v>6705867</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1412,6 +1421,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126869537</v>
+        <v>126869425</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>91779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,35 +1464,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516717</v>
+        <v>516854</v>
       </c>
       <c r="R9" t="n">
-        <v>6705867</v>
+        <v>6705833</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1522,11 +1527,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1980,42 +1980,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126869237</v>
+        <v>126869574</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516915</v>
+        <v>516694</v>
       </c>
       <c r="R14" t="n">
-        <v>6705768</v>
+        <v>6705877</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2061,17 +2065,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2090,46 +2090,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126869574</v>
+        <v>126869237</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2137,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516694</v>
+        <v>516915</v>
       </c>
       <c r="R15" t="n">
-        <v>6705877</v>
+        <v>6705768</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2175,13 +2171,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2301,46 +2301,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126869039</v>
+        <v>126869396</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>91290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2348,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516968</v>
+        <v>516879</v>
       </c>
       <c r="R17" t="n">
-        <v>6705769</v>
+        <v>6705823</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2384,11 +2375,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,37 +2402,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126869396</v>
+        <v>126869039</v>
       </c>
       <c r="B18" t="n">
-        <v>91290</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516879</v>
+        <v>516968</v>
       </c>
       <c r="R18" t="n">
-        <v>6705823</v>
+        <v>6705769</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2490,6 +2485,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126869537</v>
+        <v>126869425</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>91779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,35 +1349,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516717</v>
+        <v>516854</v>
       </c>
       <c r="R8" t="n">
-        <v>6705867</v>
+        <v>6705833</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1421,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126869425</v>
+        <v>126869537</v>
       </c>
       <c r="B9" t="n">
-        <v>91779</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,26 +1450,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516854</v>
+        <v>516717</v>
       </c>
       <c r="R9" t="n">
-        <v>6705833</v>
+        <v>6705867</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1527,6 +1522,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>126869412</v>
       </c>
       <c r="B4" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>126868956</v>
       </c>
       <c r="B5" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126869314</v>
       </c>
       <c r="B6" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126869643</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>126869425</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>126869537</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>126868998</v>
       </c>
       <c r="B11" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126869103</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,46 +1980,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126869574</v>
+        <v>126869237</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516694</v>
+        <v>516915</v>
       </c>
       <c r="R14" t="n">
-        <v>6705877</v>
+        <v>6705768</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2065,13 +2061,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2090,42 +2090,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126869237</v>
+        <v>126869574</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2133,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516915</v>
+        <v>516694</v>
       </c>
       <c r="R15" t="n">
-        <v>6705768</v>
+        <v>6705877</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2171,17 +2175,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2200,32 +2200,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126869327</v>
+        <v>126869396</v>
       </c>
       <c r="B16" t="n">
-        <v>91325</v>
+        <v>91291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516923</v>
+        <v>516879</v>
       </c>
       <c r="R16" t="n">
-        <v>6705761</v>
+        <v>6705823</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2301,32 +2301,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126869396</v>
+        <v>126869327</v>
       </c>
       <c r="B17" t="n">
-        <v>91290</v>
+        <v>91326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516879</v>
+        <v>516923</v>
       </c>
       <c r="R17" t="n">
-        <v>6705823</v>
+        <v>6705761</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2405,7 +2405,7 @@
         <v>126869039</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>126869551</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>126869457</v>
       </c>
       <c r="B20" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126869056</v>
+        <v>126869384</v>
       </c>
       <c r="B21" t="n">
-        <v>91325</v>
+        <v>57654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,26 +2748,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516953</v>
+        <v>516872</v>
       </c>
       <c r="R21" t="n">
-        <v>6705765</v>
+        <v>6705794</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2813,13 +2818,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2838,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126869384</v>
+        <v>126869056</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,31 +2858,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2881,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516872</v>
+        <v>516953</v>
       </c>
       <c r="R22" t="n">
-        <v>6705794</v>
+        <v>6705765</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2919,17 +2923,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126869384</v>
+        <v>126869056</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>91326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,31 +2748,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516872</v>
+        <v>516953</v>
       </c>
       <c r="R21" t="n">
-        <v>6705794</v>
+        <v>6705765</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2818,17 +2813,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2847,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126869056</v>
+        <v>126869384</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2858,26 +2849,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2885,10 +2881,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516953</v>
+        <v>516872</v>
       </c>
       <c r="R22" t="n">
-        <v>6705765</v>
+        <v>6705794</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2923,13 +2919,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126869425</v>
+        <v>126869537</v>
       </c>
       <c r="B8" t="n">
-        <v>91780</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,26 +1349,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516854</v>
+        <v>516717</v>
       </c>
       <c r="R8" t="n">
-        <v>6705833</v>
+        <v>6705867</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1412,6 +1421,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126869537</v>
+        <v>126869425</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>91780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,35 +1464,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516717</v>
+        <v>516854</v>
       </c>
       <c r="R9" t="n">
-        <v>6705867</v>
+        <v>6705833</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1522,11 +1527,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>126869412</v>
       </c>
       <c r="B4" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>126868956</v>
       </c>
       <c r="B5" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126869314</v>
       </c>
       <c r="B6" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126869643</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126869537</v>
+        <v>126869425</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>91784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,35 +1349,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516717</v>
+        <v>516854</v>
       </c>
       <c r="R8" t="n">
-        <v>6705867</v>
+        <v>6705833</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1421,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126869425</v>
+        <v>126869537</v>
       </c>
       <c r="B9" t="n">
-        <v>91780</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,26 +1450,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516854</v>
+        <v>516717</v>
       </c>
       <c r="R9" t="n">
-        <v>6705833</v>
+        <v>6705867</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1527,6 +1522,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,7 +1557,7 @@
         <v>126869449</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>126868998</v>
       </c>
       <c r="B11" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126869103</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>126869197</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>126869237</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>126869574</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,37 +2200,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126869396</v>
+        <v>126869039</v>
       </c>
       <c r="B16" t="n">
-        <v>91291</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2238,10 +2247,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516879</v>
+        <v>516968</v>
       </c>
       <c r="R16" t="n">
-        <v>6705823</v>
+        <v>6705769</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2274,6 +2283,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,7 +2318,7 @@
         <v>126869327</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,46 +2416,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126869039</v>
+        <v>126869396</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>91295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516968</v>
+        <v>516879</v>
       </c>
       <c r="R18" t="n">
-        <v>6705769</v>
+        <v>6705823</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2485,11 +2490,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,7 +2520,7 @@
         <v>126869551</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>126869457</v>
       </c>
       <c r="B20" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>126869056</v>
       </c>
       <c r="B21" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>126869384</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -2200,46 +2200,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126869039</v>
+        <v>126869396</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>91295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2247,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516968</v>
+        <v>516879</v>
       </c>
       <c r="R16" t="n">
-        <v>6705769</v>
+        <v>6705823</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2283,11 +2274,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,37 +2301,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126869327</v>
+        <v>126869039</v>
       </c>
       <c r="B17" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2353,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516923</v>
+        <v>516968</v>
       </c>
       <c r="R17" t="n">
-        <v>6705761</v>
+        <v>6705769</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2389,6 +2384,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,32 +2416,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126869396</v>
+        <v>126869327</v>
       </c>
       <c r="B18" t="n">
-        <v>91295</v>
+        <v>91330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516879</v>
+        <v>516923</v>
       </c>
       <c r="R18" t="n">
-        <v>6705823</v>
+        <v>6705761</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>126869643</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126869425</v>
+        <v>126869537</v>
       </c>
       <c r="B8" t="n">
-        <v>91784</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,26 +1349,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516854</v>
+        <v>516717</v>
       </c>
       <c r="R8" t="n">
-        <v>6705833</v>
+        <v>6705867</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1412,6 +1421,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126869537</v>
+        <v>126869425</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>91784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,35 +1464,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516717</v>
+        <v>516854</v>
       </c>
       <c r="R9" t="n">
-        <v>6705867</v>
+        <v>6705833</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1522,11 +1527,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1763,7 +1763,7 @@
         <v>126869103</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>126869574</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,32 +2200,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126869396</v>
+        <v>126869327</v>
       </c>
       <c r="B16" t="n">
-        <v>91295</v>
+        <v>91330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516879</v>
+        <v>516923</v>
       </c>
       <c r="R16" t="n">
-        <v>6705823</v>
+        <v>6705761</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2304,7 +2304,7 @@
         <v>126869039</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,32 +2416,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126869327</v>
+        <v>126869396</v>
       </c>
       <c r="B18" t="n">
-        <v>91330</v>
+        <v>91295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516923</v>
+        <v>516879</v>
       </c>
       <c r="R18" t="n">
-        <v>6705761</v>
+        <v>6705823</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2520,7 +2520,7 @@
         <v>126869551</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126869056</v>
+        <v>126869384</v>
       </c>
       <c r="B21" t="n">
-        <v>91330</v>
+        <v>57658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,26 +2748,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516953</v>
+        <v>516872</v>
       </c>
       <c r="R21" t="n">
-        <v>6705765</v>
+        <v>6705794</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2813,13 +2818,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2838,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126869384</v>
+        <v>126869056</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,31 +2858,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2881,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516872</v>
+        <v>516953</v>
       </c>
       <c r="R22" t="n">
-        <v>6705794</v>
+        <v>6705765</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2919,17 +2923,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -2301,46 +2301,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126869039</v>
+        <v>126869396</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>91295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2348,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516968</v>
+        <v>516879</v>
       </c>
       <c r="R17" t="n">
-        <v>6705769</v>
+        <v>6705823</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2384,11 +2375,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,37 +2402,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126869396</v>
+        <v>126869039</v>
       </c>
       <c r="B18" t="n">
-        <v>91295</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516879</v>
+        <v>516968</v>
       </c>
       <c r="R18" t="n">
-        <v>6705823</v>
+        <v>6705769</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2490,6 +2485,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>126869412</v>
       </c>
       <c r="B4" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>126868956</v>
       </c>
       <c r="B5" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126869314</v>
       </c>
       <c r="B6" t="n">
-        <v>91626</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126869643</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126869537</v>
+        <v>126869425</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>91773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,35 +1349,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516717</v>
+        <v>516854</v>
       </c>
       <c r="R8" t="n">
-        <v>6705867</v>
+        <v>6705833</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1421,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126869425</v>
+        <v>126869537</v>
       </c>
       <c r="B9" t="n">
-        <v>91784</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,26 +1450,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516854</v>
+        <v>516717</v>
       </c>
       <c r="R9" t="n">
-        <v>6705833</v>
+        <v>6705867</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1527,6 +1522,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,7 +1557,7 @@
         <v>126869449</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>126868998</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126869103</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>126869197</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,42 +1980,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126869237</v>
+        <v>126869574</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516915</v>
+        <v>516694</v>
       </c>
       <c r="R14" t="n">
-        <v>6705768</v>
+        <v>6705877</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2061,17 +2065,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2090,46 +2090,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126869574</v>
+        <v>126869237</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2137,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516694</v>
+        <v>516915</v>
       </c>
       <c r="R15" t="n">
-        <v>6705877</v>
+        <v>6705768</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2175,13 +2171,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>126869327</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>126869396</v>
       </c>
       <c r="B17" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>126869039</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>126869551</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>126869457</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>91337</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126869384</v>
+        <v>126869056</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>91319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,31 +2748,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516872</v>
+        <v>516953</v>
       </c>
       <c r="R21" t="n">
-        <v>6705794</v>
+        <v>6705765</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2818,17 +2813,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2847,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126869056</v>
+        <v>126869384</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>57654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2858,26 +2849,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2885,10 +2881,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516953</v>
+        <v>516872</v>
       </c>
       <c r="R22" t="n">
-        <v>6705765</v>
+        <v>6705794</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2923,13 +2919,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -919,7 +919,7 @@
         <v>126869412</v>
       </c>
       <c r="B4" t="n">
-        <v>91319</v>
+        <v>91330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>126868956</v>
       </c>
       <c r="B5" t="n">
-        <v>91284</v>
+        <v>91295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126869314</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
+        <v>91626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126869643</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126869425</v>
+        <v>126869537</v>
       </c>
       <c r="B8" t="n">
-        <v>91773</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1349,26 +1349,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516854</v>
+        <v>516717</v>
       </c>
       <c r="R8" t="n">
-        <v>6705833</v>
+        <v>6705867</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1412,6 +1421,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126869537</v>
+        <v>126869425</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>91784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,35 +1464,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516717</v>
+        <v>516854</v>
       </c>
       <c r="R9" t="n">
-        <v>6705867</v>
+        <v>6705833</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1524,16 +1529,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
@@ -1557,7 +1557,7 @@
         <v>126869449</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>126868998</v>
       </c>
       <c r="B11" t="n">
-        <v>91319</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>126869103</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>126869197</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -1980,46 +1980,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126869574</v>
+        <v>126869237</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516694</v>
+        <v>516915</v>
       </c>
       <c r="R14" t="n">
-        <v>6705877</v>
+        <v>6705768</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2065,13 +2061,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2090,42 +2090,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126869237</v>
+        <v>126869574</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2133,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516915</v>
+        <v>516694</v>
       </c>
       <c r="R15" t="n">
-        <v>6705768</v>
+        <v>6705877</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2171,17 +2175,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>126869327</v>
       </c>
       <c r="B16" t="n">
-        <v>91319</v>
+        <v>91330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>126869396</v>
       </c>
       <c r="B17" t="n">
-        <v>91284</v>
+        <v>91295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>126869039</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>126869551</v>
       </c>
       <c r="B19" t="n">
-        <v>98436</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>126869457</v>
       </c>
       <c r="B20" t="n">
-        <v>91337</v>
+        <v>91348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126869056</v>
+        <v>126869384</v>
       </c>
       <c r="B21" t="n">
-        <v>91319</v>
+        <v>57658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,26 +2748,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516953</v>
+        <v>516872</v>
       </c>
       <c r="R21" t="n">
-        <v>6705765</v>
+        <v>6705794</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2813,13 +2818,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2838,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126869384</v>
+        <v>126869056</v>
       </c>
       <c r="B22" t="n">
-        <v>57654</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,31 +2858,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2881,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516872</v>
+        <v>516953</v>
       </c>
       <c r="R22" t="n">
-        <v>6705794</v>
+        <v>6705765</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2919,17 +2923,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -2951,7 +2951,7 @@
         <v>131219383</v>
       </c>
       <c r="B23" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -2951,7 +2951,7 @@
         <v>131219383</v>
       </c>
       <c r="B23" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -3061,7 +3061,7 @@
         <v>132420616</v>
       </c>
       <c r="B24" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3944,6 +3944,115 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133851021</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bjusan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>516583</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6705983</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -3949,7 +3949,7 @@
         <v>133851021</v>
       </c>
       <c r="B32" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -3949,7 +3949,7 @@
         <v>133851021</v>
       </c>
       <c r="B32" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110550894</v>
+        <v>126869314</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,14 +713,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster Bjusan, Dlr</t>
+          <t>Bjusan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516802.9819914385</v>
+        <v>516915</v>
       </c>
       <c r="R2" t="n">
-        <v>6705812.283722766</v>
+        <v>6705761</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,29 +747,19 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -795,62 +780,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125630629</v>
+        <v>110550894</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Reptjätnsbergets naturreservat, Reptjätnsbergets naturreservat, Dlr</t>
+          <t>Väster Bjusan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516723</v>
+        <v>516803</v>
       </c>
       <c r="R3" t="n">
-        <v>6705904</v>
+        <v>6705812</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,52 +852,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126869412</v>
+        <v>126868998</v>
       </c>
       <c r="B4" t="n">
-        <v>91330</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516865</v>
+        <v>517011</v>
       </c>
       <c r="R4" t="n">
-        <v>6705828</v>
+        <v>6705728</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1017,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126868956</v>
+        <v>126869056</v>
       </c>
       <c r="B5" t="n">
-        <v>91295</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517002</v>
+        <v>516953</v>
       </c>
       <c r="R5" t="n">
-        <v>6705734</v>
+        <v>6705765</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1118,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126869314</v>
+        <v>126869327</v>
       </c>
       <c r="B6" t="n">
-        <v>91626</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,28 +1098,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1160,7 +1125,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516915</v>
+        <v>516923</v>
       </c>
       <c r="R6" t="n">
         <v>6705761</v>
@@ -1223,46 +1188,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126869643</v>
+        <v>126869412</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1270,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516614</v>
+        <v>516865</v>
       </c>
       <c r="R7" t="n">
-        <v>6705946</v>
+        <v>6705828</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1306,11 +1262,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>17 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,46 +1289,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126869537</v>
+        <v>126869425</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1385,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516717</v>
+        <v>516854</v>
       </c>
       <c r="R8" t="n">
-        <v>6705867</v>
+        <v>6705833</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1423,16 +1365,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
@@ -1453,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126869425</v>
+        <v>126868956</v>
       </c>
       <c r="B9" t="n">
-        <v>91784</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516854</v>
+        <v>517002</v>
       </c>
       <c r="R9" t="n">
-        <v>6705833</v>
+        <v>6705734</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1533,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
@@ -1554,42 +1491,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126869449</v>
+        <v>126869396</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1597,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516846</v>
+        <v>516879</v>
       </c>
       <c r="R10" t="n">
-        <v>6705888</v>
+        <v>6705823</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1639,8 +1571,9 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1659,37 +1592,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126868998</v>
+        <v>126869384</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1697,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517011</v>
+        <v>516872</v>
       </c>
       <c r="R11" t="n">
-        <v>6705728</v>
+        <v>6705794</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1735,13 +1673,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1760,46 +1702,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126869103</v>
+        <v>131219383</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1807,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516882</v>
+        <v>516893</v>
       </c>
       <c r="R12" t="n">
-        <v>6705747</v>
+        <v>6705745</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,17 +1775,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 blomsterstjälk</t>
+          <t>Grov äldre tall. 10 meter upp, ovalt hål, cirka 7 cm stort.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,7 +1794,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1875,27 +1812,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126869197</v>
+        <v>132420761</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1908,20 +1845,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjusan, Dlr</t>
+          <t>Bjusan., Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516904</v>
+        <v>516632</v>
       </c>
       <c r="R13" t="n">
-        <v>6705756</v>
+        <v>6705945</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1948,19 +1885,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack nedtill död tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -1980,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126869237</v>
+        <v>126869197</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +1955,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2023,10 +1965,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516915</v>
+        <v>516904</v>
       </c>
       <c r="R14" t="n">
-        <v>6705768</v>
+        <v>6705756</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2061,16 +2003,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2090,46 +2027,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126869574</v>
+        <v>126869237</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2137,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516694</v>
+        <v>516915</v>
       </c>
       <c r="R15" t="n">
-        <v>6705877</v>
+        <v>6705768</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2175,13 +2108,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2200,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126869327</v>
+        <v>126869449</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,26 +2148,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2238,10 +2180,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516923</v>
+        <v>516846</v>
       </c>
       <c r="R16" t="n">
-        <v>6705761</v>
+        <v>6705888</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2280,9 +2222,8 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2301,48 +2242,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126869396</v>
+        <v>132420662</v>
       </c>
       <c r="B17" t="n">
-        <v>91295</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bjusan, Dlr</t>
+          <t>Bjusan., Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516879</v>
+        <v>516608</v>
       </c>
       <c r="R17" t="n">
-        <v>6705823</v>
+        <v>6705974</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2369,12 +2315,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2383,7 +2334,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2402,46 +2352,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126869039</v>
+        <v>132420690</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2449,10 +2395,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516968</v>
+        <v>516609</v>
       </c>
       <c r="R18" t="n">
-        <v>6705769</v>
+        <v>6705961</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2479,17 +2425,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>3 blomsterstjälkar</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,7 +2444,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2517,46 +2462,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126869551</v>
+        <v>132420775</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2564,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>516706</v>
+        <v>516764</v>
       </c>
       <c r="R19" t="n">
-        <v>6705843</v>
+        <v>6705910</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2594,17 +2535,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>21 blomsterstjälkar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,7 +2554,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126869457</v>
+        <v>132711910</v>
       </c>
       <c r="B20" t="n">
-        <v>91348</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,30 +2583,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2674,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516801</v>
+        <v>516633</v>
       </c>
       <c r="R20" t="n">
-        <v>6705837</v>
+        <v>6705909</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2704,12 +2645,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,7 +2664,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2737,10 +2682,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126869384</v>
+        <v>132711931</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,16 +2693,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2770,7 +2715,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2780,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516872</v>
+        <v>516645</v>
       </c>
       <c r="R21" t="n">
-        <v>6705794</v>
+        <v>6705901</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2810,17 +2755,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>hack nedtill på gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2847,10 +2792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126869056</v>
+        <v>132711971</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2858,26 +2803,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2885,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516953</v>
+        <v>516671</v>
       </c>
       <c r="R22" t="n">
-        <v>6705765</v>
+        <v>6705881</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2915,12 +2865,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,7 +2884,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2948,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131219383</v>
+        <v>132420616</v>
       </c>
       <c r="B23" t="n">
-        <v>57896</v>
+        <v>58136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,29 +2913,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2991,13 +2953,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516893</v>
+        <v>516590</v>
       </c>
       <c r="R23" t="n">
-        <v>6705745</v>
+        <v>6705969</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3021,17 +2983,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Grov äldre tall. 10 meter upp, ovalt hål, cirka 7 cm stort.</t>
+          <t>De uppehöll sig en stund vid rapportören, var upprörda och försökte jaga bort rapportören med upprörda läten.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3058,10 +3020,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132420616</v>
+        <v>133851021</v>
       </c>
       <c r="B24" t="n">
-        <v>58118</v>
+        <v>58136</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,15 +3050,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
@@ -3109,10 +3067,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516590</v>
+        <v>516583</v>
       </c>
       <c r="R24" t="n">
-        <v>6705969</v>
+        <v>6705983</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3139,17 +3097,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>De uppehöll sig en stund vid rapportören, var upprörda och försökte jaga bort rapportören med upprörda läten.</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,56 +3129,62 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132420662</v>
+        <v>125630629</v>
       </c>
       <c r="B25" t="n">
-        <v>57957</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bjusan., Dlr</t>
+          <t>Reptjätnsbergets naturreservat, Reptjätnsbergets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516608</v>
+        <v>516723</v>
       </c>
       <c r="R25" t="n">
-        <v>6705974</v>
+        <v>6705904</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3249,17 +3208,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,54 +3238,58 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132420775</v>
+        <v>126869039</v>
       </c>
       <c r="B26" t="n">
-        <v>57957</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3329,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516764</v>
+        <v>516968</v>
       </c>
       <c r="R26" t="n">
-        <v>6705910</v>
+        <v>6705769</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3359,17 +3327,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,6 +3346,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3396,42 +3365,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132420690</v>
+        <v>126869103</v>
       </c>
       <c r="B27" t="n">
-        <v>57957</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3439,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516609</v>
+        <v>516882</v>
       </c>
       <c r="R27" t="n">
-        <v>6705961</v>
+        <v>6705747</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3469,17 +3442,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>1 blomsterstjälk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,6 +3461,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3506,53 +3480,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132420761</v>
+        <v>126869537</v>
       </c>
       <c r="B28" t="n">
-        <v>57954</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjusan., Dlr</t>
+          <t>Bjusan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>516632</v>
+        <v>516717</v>
       </c>
       <c r="R28" t="n">
-        <v>6705945</v>
+        <v>6705867</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3579,17 +3557,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Födosökshack nedtill död tall.</t>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3598,6 +3576,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3616,42 +3595,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132711931</v>
+        <v>126869551</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3659,10 +3642,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>516645</v>
+        <v>516706</v>
       </c>
       <c r="R29" t="n">
-        <v>6705901</v>
+        <v>6705843</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3689,17 +3672,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>21 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,6 +3691,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3726,42 +3710,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132711910</v>
+        <v>126869574</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3769,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>516633</v>
+        <v>516694</v>
       </c>
       <c r="R30" t="n">
-        <v>6705909</v>
+        <v>6705877</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3799,17 +3787,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3818,6 +3801,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3836,42 +3820,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132711971</v>
+        <v>126869643</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3879,10 +3867,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>516671</v>
+        <v>516614</v>
       </c>
       <c r="R31" t="n">
-        <v>6705881</v>
+        <v>6705946</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3909,17 +3897,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>17 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3928,6 +3916,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3943,115 +3932,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>133851021</v>
-      </c>
-      <c r="B32" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Bjusan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>516583</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6705983</v>
-      </c>
-      <c r="S32" t="n">
-        <v>50</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869314</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110550894</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868998</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869056</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869327</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869412</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869425</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868956</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869396</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869384</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131219383</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132420761</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2024,6 +2089,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869197</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2134,6 +2204,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869237</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2239,6 +2314,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869449</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2349,6 +2429,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132420662</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2459,6 +2544,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132420690</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2569,6 +2659,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132420775</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2679,6 +2774,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711910</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2789,6 +2889,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711931</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2899,6 +3004,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132711971</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3017,6 +3127,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132420616</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3126,6 +3241,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851021</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3247,6 +3367,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125630629</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3362,6 +3487,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869039</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3477,6 +3607,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869103</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3592,6 +3727,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869537</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3707,6 +3847,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869551</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3817,6 +3962,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869574</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3932,8 +4082,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1430,36 +1430,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126868956</v>
+        <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>91872</v>
+        <v>93347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1468,13 +1476,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517002</v>
+        <v>516876</v>
       </c>
       <c r="R9" t="n">
-        <v>6705734</v>
+        <v>6705849</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,12 +1506,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,13 +1538,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126868956</t>
+          <t>https://artportalen.se/Sighting/136023855</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126869396</v>
+        <v>126868956</v>
       </c>
       <c r="B10" t="n">
         <v>91872</v>
@@ -1574,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516879</v>
+        <v>517002</v>
       </c>
       <c r="R10" t="n">
-        <v>6705823</v>
+        <v>6705734</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1636,16 +1644,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869396</t>
+          <t>https://artportalen.se/Sighting/126868956</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126869384</v>
+        <v>126869396</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,31 +1661,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516872</v>
+        <v>516879</v>
       </c>
       <c r="R11" t="n">
-        <v>6705794</v>
+        <v>6705823</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1723,17 +1726,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1751,13 +1750,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869384</t>
+          <t>https://artportalen.se/Sighting/126869396</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131219383</v>
+        <v>126869384</v>
       </c>
       <c r="B12" t="n">
         <v>57950</v>
@@ -1790,7 +1789,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1800,13 +1799,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516893</v>
+        <v>516872</v>
       </c>
       <c r="R12" t="n">
-        <v>6705745</v>
+        <v>6705794</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1830,17 +1829,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Grov äldre tall. 10 meter upp, ovalt hål, cirka 7 cm stort.</t>
+          <t>hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,16 +1865,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131219383</t>
+          <t>https://artportalen.se/Sighting/126869384</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132420761</v>
+        <v>131219383</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,23 +1904,23 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjusan., Dlr</t>
+          <t>Bjusan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516632</v>
+        <v>516893</v>
       </c>
       <c r="R13" t="n">
-        <v>6705945</v>
+        <v>6705745</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1945,17 +1944,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Födosökshack nedtill död tall.</t>
+          <t>Grov äldre tall. 10 meter upp, ovalt hål, cirka 7 cm stort.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1981,33 +1980,33 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132420761</t>
+          <t>https://artportalen.se/Sighting/131219383</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126869197</v>
+        <v>132420761</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2020,20 +2019,20 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjusan, Dlr</t>
+          <t>Bjusan., Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516904</v>
+        <v>516632</v>
       </c>
       <c r="R14" t="n">
-        <v>6705756</v>
+        <v>6705945</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2060,19 +2059,24 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack nedtill död tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2091,33 +2095,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869197</t>
+          <t>https://artportalen.se/Sighting/132420761</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126869237</v>
+        <v>136023953</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2130,7 +2134,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2140,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516915</v>
+        <v>516946</v>
       </c>
       <c r="R15" t="n">
-        <v>6705768</v>
+        <v>6705708</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2170,17 +2174,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>födosökshack nedtill död gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,13 +2210,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869237</t>
+          <t>https://artportalen.se/Sighting/136023953</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126869449</v>
+        <v>126869197</v>
       </c>
       <c r="B16" t="n">
         <v>57953</v>
@@ -2255,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516846</v>
+        <v>516904</v>
       </c>
       <c r="R16" t="n">
-        <v>6705888</v>
+        <v>6705756</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2316,16 +2320,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869449</t>
+          <t>https://artportalen.se/Sighting/126869197</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132420662</v>
+        <v>126869237</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,14 +2365,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bjusan., Dlr</t>
+          <t>Bjusan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516608</v>
+        <v>516915</v>
       </c>
       <c r="R17" t="n">
-        <v>6705974</v>
+        <v>6705768</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2395,17 +2399,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,16 +2435,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132420662</t>
+          <t>https://artportalen.se/Sighting/126869237</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132420690</v>
+        <v>126869449</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,7 +2474,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2480,10 +2484,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516609</v>
+        <v>516846</v>
       </c>
       <c r="R18" t="n">
-        <v>6705961</v>
+        <v>6705888</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2510,24 +2514,19 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2546,13 +2545,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132420690</t>
+          <t>https://artportalen.se/Sighting/126869449</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132420775</v>
+        <v>132420662</v>
       </c>
       <c r="B19" t="n">
         <v>57975</v>
@@ -2591,14 +2590,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjusan, Dlr</t>
+          <t>Bjusan., Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>516764</v>
+        <v>516608</v>
       </c>
       <c r="R19" t="n">
-        <v>6705910</v>
+        <v>6705974</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2635,7 +2634,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,13 +2660,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132420775</t>
+          <t>https://artportalen.se/Sighting/132420662</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132711910</v>
+        <v>132420690</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2710,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516633</v>
+        <v>516609</v>
       </c>
       <c r="R20" t="n">
-        <v>6705909</v>
+        <v>6705961</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2740,12 +2739,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2776,13 +2775,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132711910</t>
+          <t>https://artportalen.se/Sighting/132420690</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132711931</v>
+        <v>132420775</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -2825,10 +2824,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>516645</v>
+        <v>516764</v>
       </c>
       <c r="R21" t="n">
-        <v>6705901</v>
+        <v>6705910</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2855,17 +2854,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,13 +2890,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132711931</t>
+          <t>https://artportalen.se/Sighting/132420775</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132711971</v>
+        <v>132711910</v>
       </c>
       <c r="B22" t="n">
         <v>57975</v>
@@ -2940,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516671</v>
+        <v>516633</v>
       </c>
       <c r="R22" t="n">
-        <v>6705881</v>
+        <v>6705909</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2980,7 +2979,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,16 +3005,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132711971</t>
+          <t>https://artportalen.se/Sighting/132711910</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132420616</v>
+        <v>132711931</v>
       </c>
       <c r="B23" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3023,37 +3022,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3063,10 +3054,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>516590</v>
+        <v>516645</v>
       </c>
       <c r="R23" t="n">
-        <v>6705969</v>
+        <v>6705901</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3093,17 +3084,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>De uppehöll sig en stund vid rapportören, var upprörda och försökte jaga bort rapportören med upprörda läten.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3129,16 +3120,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132420616</t>
+          <t>https://artportalen.se/Sighting/132711931</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133851021</v>
+        <v>132711971</v>
       </c>
       <c r="B24" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3146,33 +3137,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3182,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>516583</v>
+        <v>516671</v>
       </c>
       <c r="R24" t="n">
-        <v>6705983</v>
+        <v>6705881</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3212,12 +3199,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,68 +3235,62 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133851021</t>
+          <t>https://artportalen.se/Sighting/132711971</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125630629</v>
+        <v>136023834</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>57167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Reptjätnsbergets naturreservat, Reptjätnsbergets naturreservat, Dlr</t>
+          <t>Bjusan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516723</v>
+        <v>516886</v>
       </c>
       <c r="R25" t="n">
-        <v>6705904</v>
+        <v>6705780</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3328,22 +3314,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3358,63 +3334,67 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125630629</t>
+          <t>https://artportalen.se/Sighting/136023834</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126869039</v>
+        <v>132420616</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3422,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>516968</v>
+        <v>516590</v>
       </c>
       <c r="R26" t="n">
-        <v>6705769</v>
+        <v>6705969</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3452,17 +3432,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>3 blomsterstjälkar</t>
+          <t>De uppehöll sig en stund vid rapportören, var upprörda och försökte jaga bort rapportören med upprörda läten.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3471,7 +3451,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3489,52 +3468,52 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869039</t>
+          <t>https://artportalen.se/Sighting/132420616</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126869103</v>
+        <v>133851021</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3542,10 +3521,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516882</v>
+        <v>516583</v>
       </c>
       <c r="R27" t="n">
-        <v>6705747</v>
+        <v>6705983</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3572,17 +3551,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 blomsterstjälk</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,7 +3565,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3609,13 +3582,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869103</t>
+          <t>https://artportalen.se/Sighting/133851021</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126869537</v>
+        <v>125630629</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3645,30 +3618,32 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bjusan, Dlr</t>
+          <t>Reptjätnsbergets naturreservat, Reptjätnsbergets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>516717</v>
+        <v>516723</v>
       </c>
       <c r="R28" t="n">
-        <v>6705867</v>
+        <v>6705904</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3692,17 +3667,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>8 blomsterstjälkar</t>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,31 +3691,30 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869537</t>
+          <t>https://artportalen.se/Sighting/125630629</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126869551</v>
+        <v>126869039</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -3765,7 +3744,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3782,10 +3761,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>516706</v>
+        <v>516968</v>
       </c>
       <c r="R29" t="n">
-        <v>6705843</v>
+        <v>6705769</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3822,7 +3801,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>21 blomsterstjälkar</t>
+          <t>3 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3849,13 +3828,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869551</t>
+          <t>https://artportalen.se/Sighting/126869039</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126869574</v>
+        <v>126869103</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -3885,7 +3864,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3902,10 +3881,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>516694</v>
+        <v>516882</v>
       </c>
       <c r="R30" t="n">
-        <v>6705877</v>
+        <v>6705747</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3940,6 +3919,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 blomsterstjälk</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3964,13 +3948,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126869574</t>
+          <t>https://artportalen.se/Sighting/126869103</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126869643</v>
+        <v>126869537</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -4000,7 +3984,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4017,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>516614</v>
+        <v>516717</v>
       </c>
       <c r="R31" t="n">
-        <v>6705946</v>
+        <v>6705867</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4057,7 +4041,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>17 blomsterstjälkar</t>
+          <t>8 blomsterstjälkar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4083,6 +4067,361 @@
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869537</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126869551</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bjusan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>516706</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6705843</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>21 blomsterstjälkar</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869551</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126869574</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bjusan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>516694</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6705877</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126869574</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126869643</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bjusan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>516614</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6705946</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>17 blomsterstjälkar</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126869643</t>
         </is>
@@ -4120,6 +4459,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136023953</v>
       </c>
       <c r="B15" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136023834</v>
       </c>
       <c r="B25" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136023953</v>
       </c>
       <c r="B15" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136023834</v>
       </c>
       <c r="B25" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136023953</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136023834</v>
       </c>
       <c r="B25" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136023953</v>
       </c>
       <c r="B15" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136023834</v>
       </c>
       <c r="B25" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136023953</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136023834</v>
       </c>
       <c r="B25" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136023953</v>
       </c>
       <c r="B15" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>136023834</v>
       </c>
       <c r="B25" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 28671-2025 artfynd.xlsx
+++ b/artfynd/A 28671-2025 artfynd.xlsx
@@ -1433,7 +1433,7 @@
         <v>136023855</v>
       </c>
       <c r="B9" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
